--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\MyModels\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F902FFA0-E1CE-4E6E-8119-38C1420E578C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB83B44-C4BC-42D0-BE1C-7A75B78FC760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Amit Kanudia:</t>
         </r>
@@ -57,7 +57,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 29-07-2025
@@ -74,7 +74,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Amit Kanudia:</t>
         </r>
@@ -83,7 +83,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 03-08-2025
@@ -373,7 +373,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,14 +392,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -447,6 +447,12 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -552,7 +558,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -569,15 +575,13 @@
     <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -971,40 +975,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.59765625" customWidth="1"/>
-    <col min="5" max="5" width="9.53125" customWidth="1"/>
-    <col min="6" max="7" width="9.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.06640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.19921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" customWidth="1"/>
+    <col min="6" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.77734375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="24" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="23.73046875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="AB1">
         <v>1.1000000000000001</v>
       </c>
@@ -1012,7 +1016,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="F2" s="6" t="s">
         <v>50</v>
       </c>
@@ -1029,7 +1033,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -1077,7 +1081,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -1100,7 +1104,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>0.28000000000000003</v>
       </c>
@@ -1132,7 +1136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>12</v>
       </c>
@@ -1207,7 +1211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>19</v>
       </c>
@@ -1277,7 +1281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="F9" t="s">
         <v>23</v>
       </c>
@@ -1345,7 +1349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:38" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F10" t="s">
         <v>9</v>
       </c>
@@ -1362,7 +1366,7 @@
         <v>0.14275360852558924</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:38" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
         <v>12</v>
       </c>
@@ -1379,7 +1383,7 @@
         <v>0.21594436217582091</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>26</v>
       </c>
@@ -1387,7 +1391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -1428,7 +1432,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -1463,27 +1467,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="L16" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L17" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L18" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>27</v>
       </c>
@@ -1503,7 +1507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>32</v>
       </c>
@@ -1521,7 +1525,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>32</v>
       </c>
@@ -1539,7 +1543,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>32</v>
       </c>
@@ -1557,7 +1561,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>44</v>
       </c>
@@ -1571,7 +1575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>44</v>
       </c>
@@ -1585,7 +1589,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>49</v>
       </c>
@@ -1600,7 +1604,7 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>66</v>
       </c>
@@ -1611,7 +1615,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>68</v>
       </c>
@@ -1622,12 +1626,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>13</v>
       </c>
@@ -1644,7 +1648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>39</v>
       </c>
@@ -1658,7 +1662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
         <v>9</v>
       </c>
@@ -1666,7 +1670,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>41</v>
       </c>
@@ -1680,7 +1684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
         <v>12</v>
       </c>
@@ -1697,101 +1701,101 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="10.59765625" customWidth="1"/>
-    <col min="8" max="8" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B10" s="17" t="s">
+    <row r="10" spans="1:10" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="17" t="s">
+      <c r="J10" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B11" s="18" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="16">
         <v>7</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="13">
         <v>10</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="16">
         <v>4</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="16">
         <v>6</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="17">
         <v>0.1</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="17">
         <v>0.3</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="18">
         <v>0</v>
       </c>
-      <c r="J11" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -1817,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1847,7 +1851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1877,7 +1881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1907,7 +1911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1931,7 +1935,7 @@
       </c>
       <c r="G23">
         <f>J11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>4</v>
@@ -1949,12 +1953,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC33DFE9-8C65-4A33-8FAE-96323628CE2A}">
   <dimension ref="A1:D698"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:4" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
         <v>50</v>
       </c>
@@ -1968,7 +1972,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>55</v>
       </c>
@@ -1982,7 +1986,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
@@ -1996,7 +2000,7 @@
         <v>26.28</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>8</v>
       </c>
@@ -2010,7 +2014,7 @@
         <v>101.36</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>6</v>
       </c>
@@ -2024,7 +2028,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>19</v>
       </c>
@@ -2038,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>23</v>
       </c>
@@ -2052,7 +2056,7 @@
         <v>91.43</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>55</v>
       </c>
@@ -2066,7 +2070,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>9</v>
       </c>
@@ -2080,7 +2084,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>12</v>
       </c>
@@ -2094,7 +2098,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>55</v>
       </c>
@@ -2108,7 +2112,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>5</v>
       </c>
@@ -2122,7 +2126,7 @@
         <v>31.73</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>8</v>
       </c>
@@ -2136,7 +2140,7 @@
         <v>104.19</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>6</v>
       </c>
@@ -2150,7 +2154,7 @@
         <v>46.81</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>19</v>
       </c>
@@ -2164,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>23</v>
       </c>
@@ -2178,7 +2182,7 @@
         <v>81.63</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>55</v>
       </c>
@@ -2192,7 +2196,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>9</v>
       </c>
@@ -2206,7 +2210,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>12</v>
       </c>
@@ -2220,7 +2224,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>55</v>
       </c>
@@ -2234,7 +2238,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>5</v>
       </c>
@@ -2248,7 +2252,7 @@
         <v>35.450000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>8</v>
       </c>
@@ -2262,7 +2266,7 @@
         <v>99.41</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>6</v>
       </c>
@@ -2276,7 +2280,7 @@
         <v>39.520000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>19</v>
       </c>
@@ -2290,7 +2294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>23</v>
       </c>
@@ -2304,7 +2308,7 @@
         <v>94.36</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>55</v>
       </c>
@@ -2318,7 +2322,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>9</v>
       </c>
@@ -2332,7 +2336,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>12</v>
       </c>
@@ -2346,7 +2350,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>55</v>
       </c>
@@ -2360,7 +2364,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>5</v>
       </c>
@@ -2374,7 +2378,7 @@
         <v>38.81</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>8</v>
       </c>
@@ -2388,7 +2392,7 @@
         <v>117.3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>6</v>
       </c>
@@ -2402,7 +2406,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>19</v>
       </c>
@@ -2416,7 +2420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
         <v>23</v>
       </c>
@@ -2430,7 +2434,7 @@
         <v>83.3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>55</v>
       </c>
@@ -2444,7 +2448,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>9</v>
       </c>
@@ -2458,7 +2462,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>12</v>
       </c>
@@ -2472,7 +2476,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
         <v>55</v>
       </c>
@@ -2486,7 +2490,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>5</v>
       </c>
@@ -2500,7 +2504,7 @@
         <v>45.52</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
         <v>8</v>
       </c>
@@ -2514,7 +2518,7 @@
         <v>129.84</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>6</v>
       </c>
@@ -2528,7 +2532,7 @@
         <v>42.34</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
         <v>19</v>
       </c>
@@ -2542,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>23</v>
       </c>
@@ -2556,7 +2560,7 @@
         <v>64.48</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
         <v>55</v>
       </c>
@@ -2570,7 +2574,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>9</v>
       </c>
@@ -2584,7 +2588,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>12</v>
       </c>
@@ -2598,7 +2602,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
         <v>55</v>
       </c>
@@ -2612,7 +2616,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>5</v>
       </c>
@@ -2626,7 +2630,7 @@
         <v>43.61</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>8</v>
       </c>
@@ -2640,7 +2644,7 @@
         <v>149.33000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>6</v>
       </c>
@@ -2654,7 +2658,7 @@
         <v>36.07</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
         <v>19</v>
       </c>
@@ -2668,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>23</v>
       </c>
@@ -2682,7 +2686,7 @@
         <v>53.26</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
         <v>55</v>
       </c>
@@ -2696,7 +2700,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
         <v>9</v>
       </c>
@@ -2710,7 +2714,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
         <v>12</v>
       </c>
@@ -2724,7 +2728,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
         <v>55</v>
       </c>
@@ -2738,7 +2742,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
         <v>5</v>
       </c>
@@ -2752,7 +2756,7 @@
         <v>44.21</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
         <v>8</v>
       </c>
@@ -2766,7 +2770,7 @@
         <v>158.13999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
         <v>6</v>
       </c>
@@ -2780,7 +2784,7 @@
         <v>36.99</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
         <v>19</v>
       </c>
@@ -2794,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
         <v>23</v>
       </c>
@@ -2808,7 +2812,7 @@
         <v>52.62</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
         <v>55</v>
       </c>
@@ -2822,7 +2826,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
         <v>9</v>
       </c>
@@ -2836,7 +2840,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
         <v>12</v>
       </c>
@@ -2850,7 +2854,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="14" t="s">
         <v>55</v>
       </c>
@@ -2864,7 +2868,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
         <v>5</v>
       </c>
@@ -2878,7 +2882,7 @@
         <v>44.11</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="14" t="s">
         <v>8</v>
       </c>
@@ -2892,7 +2896,7 @@
         <v>172.71</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
         <v>6</v>
       </c>
@@ -2906,7 +2910,7 @@
         <v>32.82</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="14" t="s">
         <v>19</v>
       </c>
@@ -2920,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
         <v>23</v>
       </c>
@@ -2934,7 +2938,7 @@
         <v>41.63</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="14" t="s">
         <v>55</v>
       </c>
@@ -2948,7 +2952,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
         <v>9</v>
       </c>
@@ -2962,7 +2966,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="14" t="s">
         <v>12</v>
       </c>
@@ -2976,7 +2980,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
         <v>55</v>
       </c>
@@ -2990,7 +2994,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="14" t="s">
         <v>5</v>
       </c>
@@ -3004,7 +3008,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>8</v>
       </c>
@@ -3018,7 +3022,7 @@
         <v>172.77</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="14" t="s">
         <v>6</v>
       </c>
@@ -3032,7 +3036,7 @@
         <v>41.62</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
         <v>19</v>
       </c>
@@ -3046,7 +3050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
         <v>23</v>
       </c>
@@ -3060,7 +3064,7 @@
         <v>37.57</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
         <v>55</v>
       </c>
@@ -3074,7 +3078,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="14" t="s">
         <v>9</v>
       </c>
@@ -3088,7 +3092,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
         <v>12</v>
       </c>
@@ -3102,7 +3106,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="14" t="s">
         <v>55</v>
       </c>
@@ -3116,7 +3120,7 @@
         <v>7.56</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
         <v>5</v>
       </c>
@@ -3130,7 +3134,7 @@
         <v>39.74</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="14" t="s">
         <v>8</v>
       </c>
@@ -3144,7 +3148,7 @@
         <v>147.36000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
         <v>6</v>
       </c>
@@ -3158,7 +3162,7 @@
         <v>49.14</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="s">
         <v>19</v>
       </c>
@@ -3172,7 +3176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
         <v>23</v>
       </c>
@@ -3186,7 +3190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="14" t="s">
         <v>55</v>
       </c>
@@ -3200,7 +3204,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="12" t="s">
         <v>9</v>
       </c>
@@ -3214,7 +3218,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="14" t="s">
         <v>12</v>
       </c>
@@ -3228,7 +3232,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
         <v>55</v>
       </c>
@@ -3242,7 +3246,7 @@
         <v>9.44</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="14" t="s">
         <v>5</v>
       </c>
@@ -3256,7 +3260,7 @@
         <v>39.729999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
         <v>8</v>
       </c>
@@ -3270,7 +3274,7 @@
         <v>152.81</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="14" t="s">
         <v>6</v>
       </c>
@@ -3284,7 +3288,7 @@
         <v>51.12</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
         <v>19</v>
       </c>
@@ -3298,7 +3302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="14" t="s">
         <v>23</v>
       </c>
@@ -3312,7 +3316,7 @@
         <v>27.12</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
         <v>55</v>
       </c>
@@ -3326,7 +3330,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="14" t="s">
         <v>9</v>
       </c>
@@ -3340,7 +3344,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
         <v>12</v>
       </c>
@@ -3354,7 +3358,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="14" t="s">
         <v>55</v>
       </c>
@@ -3368,7 +3372,7 @@
         <v>10.83</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="12" t="s">
         <v>5</v>
       </c>
@@ -3382,7 +3386,7 @@
         <v>44.73</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="14" t="s">
         <v>8</v>
       </c>
@@ -3396,7 +3400,7 @@
         <v>144.6</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
         <v>6</v>
       </c>
@@ -3410,7 +3414,7 @@
         <v>45.82</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="14" t="s">
         <v>19</v>
       </c>
@@ -3424,7 +3428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
         <v>23</v>
       </c>
@@ -3438,7 +3442,7 @@
         <v>26.09</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="14" t="s">
         <v>55</v>
       </c>
@@ -3452,7 +3456,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
         <v>9</v>
       </c>
@@ -3466,7 +3470,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="14" t="s">
         <v>12</v>
       </c>
@@ -3480,7 +3484,7 @@
         <v>9.85</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="12" t="s">
         <v>55</v>
       </c>
@@ -3494,7 +3498,7 @@
         <v>12.49</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="14" t="s">
         <v>5</v>
       </c>
@@ -3508,7 +3512,7 @@
         <v>49.14</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="12" t="s">
         <v>8</v>
       </c>
@@ -3522,7 +3526,7 @@
         <v>129.13999999999999</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="14" t="s">
         <v>6</v>
       </c>
@@ -3536,7 +3540,7 @@
         <v>41.87</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="12" t="s">
         <v>19</v>
       </c>
@@ -3550,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="14" t="s">
         <v>23</v>
       </c>
@@ -3564,7 +3568,7 @@
         <v>24.75</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="12" t="s">
         <v>55</v>
       </c>
@@ -3578,7 +3582,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="14" t="s">
         <v>9</v>
       </c>
@@ -3592,7 +3596,7 @@
         <v>18.86</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
         <v>12</v>
       </c>
@@ -3606,7 +3610,7 @@
         <v>13.41</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="14" t="s">
         <v>55</v>
       </c>
@@ -3620,7 +3624,7 @@
         <v>17.079999999999998</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="12" t="s">
         <v>5</v>
       </c>
@@ -3634,7 +3638,7 @@
         <v>45.1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="14" t="s">
         <v>8</v>
       </c>
@@ -3648,7 +3652,7 @@
         <v>108.91</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
         <v>6</v>
       </c>
@@ -3662,7 +3666,7 @@
         <v>52.77</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="14" t="s">
         <v>19</v>
       </c>
@@ -3676,7 +3680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
         <v>23</v>
       </c>
@@ -3690,7 +3694,7 @@
         <v>20.010000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="14" t="s">
         <v>55</v>
       </c>
@@ -3704,7 +3708,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="12" t="s">
         <v>9</v>
       </c>
@@ -3718,7 +3722,7 @@
         <v>21.59</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="14" t="s">
         <v>12</v>
       </c>
@@ -3732,7 +3736,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="12" t="s">
         <v>55</v>
       </c>
@@ -3746,7 +3750,7 @@
         <v>18.72</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="14" t="s">
         <v>5</v>
       </c>
@@ -3760,7 +3764,7 @@
         <v>43.45</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
         <v>8</v>
       </c>
@@ -3774,7 +3778,7 @@
         <v>93.66</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="14" t="s">
         <v>6</v>
       </c>
@@ -3788,7 +3792,7 @@
         <v>58.55</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
         <v>19</v>
       </c>
@@ -3802,7 +3806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="14" t="s">
         <v>23</v>
       </c>
@@ -3816,7 +3820,7 @@
         <v>18.739999999999998</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="12" t="s">
         <v>55</v>
       </c>
@@ -3830,7 +3834,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="14" t="s">
         <v>9</v>
       </c>
@@ -3844,7 +3848,7 @@
         <v>22.31</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
         <v>12</v>
       </c>
@@ -3858,7 +3862,7 @@
         <v>15.18</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="14" t="s">
         <v>55</v>
       </c>
@@ -3872,7 +3876,7 @@
         <v>19.39</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
         <v>5</v>
       </c>
@@ -3886,7 +3890,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="14" t="s">
         <v>8</v>
       </c>
@@ -3900,7 +3904,7 @@
         <v>110.88</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
         <v>6</v>
       </c>
@@ -3914,7 +3918,7 @@
         <v>45.54</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="14" t="s">
         <v>19</v>
       </c>
@@ -3928,7 +3932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
         <v>23</v>
       </c>
@@ -3942,7 +3946,7 @@
         <v>16.73</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="14" t="s">
         <v>55</v>
       </c>
@@ -3956,7 +3960,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
         <v>9</v>
       </c>
@@ -3970,7 +3974,7 @@
         <v>22.94</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="14" t="s">
         <v>12</v>
       </c>
@@ -3984,7 +3988,7 @@
         <v>14.84</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
         <v>55</v>
       </c>
@@ -3998,7 +4002,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="14" t="s">
         <v>5</v>
       </c>
@@ -4012,7 +4016,7 @@
         <v>35.61</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
         <v>8</v>
       </c>
@@ -4026,7 +4030,7 @@
         <v>126.17</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="14" t="s">
         <v>6</v>
       </c>
@@ -4040,7 +4044,7 @@
         <v>42.43</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
         <v>19</v>
       </c>
@@ -4054,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="14" t="s">
         <v>23</v>
       </c>
@@ -4068,7 +4072,7 @@
         <v>16.16</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="12" t="s">
         <v>55</v>
       </c>
@@ -4082,7 +4086,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="14" t="s">
         <v>9</v>
       </c>
@@ -4096,7 +4100,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
         <v>12</v>
       </c>
@@ -4110,7 +4114,7 @@
         <v>17.690000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="14" t="s">
         <v>55</v>
       </c>
@@ -4124,7 +4128,7 @@
         <v>19.37</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
         <v>5</v>
       </c>
@@ -4138,7 +4142,7 @@
         <v>32.630000000000003</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="14" t="s">
         <v>8</v>
       </c>
@@ -4152,7 +4156,7 @@
         <v>140.36000000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
         <v>6</v>
       </c>
@@ -4166,7 +4170,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="14" t="s">
         <v>19</v>
       </c>
@@ -4180,7 +4184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
         <v>23</v>
       </c>
@@ -4194,7 +4198,7 @@
         <v>15.21</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="14" t="s">
         <v>55</v>
       </c>
@@ -4208,7 +4212,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="12" t="s">
         <v>9</v>
       </c>
@@ -4222,7 +4226,7 @@
         <v>24.38</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="14" t="s">
         <v>12</v>
       </c>
@@ -4236,7 +4240,7 @@
         <v>17.739999999999998</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="12" t="s">
         <v>55</v>
       </c>
@@ -4250,7 +4254,7 @@
         <v>19.14</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="14" t="s">
         <v>5</v>
       </c>
@@ -4264,7 +4268,7 @@
         <v>28.47</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
         <v>8</v>
       </c>
@@ -4278,7 +4282,7 @@
         <v>128.56</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="14" t="s">
         <v>6</v>
       </c>
@@ -4292,7 +4296,7 @@
         <v>48.79</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="12" t="s">
         <v>19</v>
       </c>
@@ -4306,7 +4310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="14" t="s">
         <v>23</v>
       </c>
@@ -4320,7 +4324,7 @@
         <v>14.62</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="12" t="s">
         <v>55</v>
       </c>
@@ -4334,7 +4338,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="14" t="s">
         <v>9</v>
       </c>
@@ -4348,7 +4352,7 @@
         <v>22.65</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="12" t="s">
         <v>12</v>
       </c>
@@ -4362,7 +4366,7 @@
         <v>17.72</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="14" t="s">
         <v>55</v>
       </c>
@@ -4376,7 +4380,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="12" t="s">
         <v>5</v>
       </c>
@@ -4390,7 +4394,7 @@
         <v>18.84</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="14" t="s">
         <v>8</v>
       </c>
@@ -4404,7 +4408,7 @@
         <v>141.69999999999999</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="12" t="s">
         <v>6</v>
       </c>
@@ -4418,7 +4422,7 @@
         <v>46.32</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="14" t="s">
         <v>19</v>
       </c>
@@ -4432,7 +4436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
         <v>23</v>
       </c>
@@ -4446,7 +4450,7 @@
         <v>13.62</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="14" t="s">
         <v>55</v>
       </c>
@@ -4460,7 +4464,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="12" t="s">
         <v>9</v>
       </c>
@@ -4474,7 +4478,7 @@
         <v>23.69</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="14" t="s">
         <v>12</v>
       </c>
@@ -4488,7 +4492,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="12" t="s">
         <v>55</v>
       </c>
@@ -4502,7 +4506,7 @@
         <v>19.62</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="14" t="s">
         <v>5</v>
       </c>
@@ -4516,7 +4520,7 @@
         <v>13.38</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
         <v>8</v>
       </c>
@@ -4530,7 +4534,7 @@
         <v>133.69999999999999</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="14" t="s">
         <v>6</v>
       </c>
@@ -4544,7 +4548,7 @@
         <v>47.55</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="12" t="s">
         <v>19</v>
       </c>
@@ -4558,7 +4562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="14" t="s">
         <v>23</v>
       </c>
@@ -4572,7 +4576,7 @@
         <v>12.83</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="12" t="s">
         <v>55</v>
       </c>
@@ -4586,7 +4590,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="14" t="s">
         <v>9</v>
       </c>
@@ -4600,7 +4604,7 @@
         <v>24.94</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
         <v>12</v>
       </c>
@@ -4614,7 +4618,7 @@
         <v>18.760000000000002</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="14" t="s">
         <v>55</v>
       </c>
@@ -4628,7 +4632,7 @@
         <v>19.059999999999999</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="12" t="s">
         <v>5</v>
       </c>
@@ -4642,7 +4646,7 @@
         <v>14.02</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="14" t="s">
         <v>8</v>
       </c>
@@ -4656,7 +4660,7 @@
         <v>144.01</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="12" t="s">
         <v>6</v>
       </c>
@@ -4670,7 +4674,7 @@
         <v>45.39</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="14" t="s">
         <v>19</v>
       </c>
@@ -4684,7 +4688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="12" t="s">
         <v>23</v>
       </c>
@@ -4698,7 +4702,7 @@
         <v>11.13</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="14" t="s">
         <v>55</v>
       </c>
@@ -4712,7 +4716,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="12" t="s">
         <v>9</v>
       </c>
@@ -4726,7 +4730,7 @@
         <v>25.04</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="14" t="s">
         <v>12</v>
       </c>
@@ -4740,7 +4744,7 @@
         <v>20.93</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="12" t="s">
         <v>55</v>
       </c>
@@ -4754,7 +4758,7 @@
         <v>17.61</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="14" t="s">
         <v>5</v>
       </c>
@@ -4768,7 +4772,7 @@
         <v>22.61</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="12" t="s">
         <v>8</v>
       </c>
@@ -4782,7 +4786,7 @@
         <v>141.47</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="14" t="s">
         <v>6</v>
       </c>
@@ -4796,7 +4800,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="12" t="s">
         <v>19</v>
       </c>
@@ -4810,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="14" t="s">
         <v>23</v>
       </c>
@@ -4824,7 +4828,7 @@
         <v>15.63</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="12" t="s">
         <v>55</v>
       </c>
@@ -4838,7 +4842,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="14" t="s">
         <v>9</v>
       </c>
@@ -4852,7 +4856,7 @@
         <v>28.12</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="12" t="s">
         <v>12</v>
       </c>
@@ -4866,7 +4870,7 @@
         <v>20.28</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="14" t="s">
         <v>55</v>
       </c>
@@ -4880,7 +4884,7 @@
         <v>16.61</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="12" t="s">
         <v>5</v>
       </c>
@@ -4894,7 +4898,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="14" t="s">
         <v>8</v>
       </c>
@@ -4908,7 +4912,7 @@
         <v>118.34</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="12" t="s">
         <v>6</v>
       </c>
@@ -4922,7 +4926,7 @@
         <v>37.94</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="14" t="s">
         <v>19</v>
       </c>
@@ -4936,7 +4940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="12" t="s">
         <v>23</v>
       </c>
@@ -4950,7 +4954,7 @@
         <v>15.54</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="14" t="s">
         <v>55</v>
       </c>
@@ -4964,7 +4968,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="12" t="s">
         <v>9</v>
       </c>
@@ -4978,7 +4982,7 @@
         <v>31.01</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="14" t="s">
         <v>12</v>
       </c>
@@ -4992,7 +4996,7 @@
         <v>23.51</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="12" t="s">
         <v>55</v>
       </c>
@@ -5006,7 +5010,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="14" t="s">
         <v>5</v>
       </c>
@@ -5020,7 +5024,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="12" t="s">
         <v>8</v>
       </c>
@@ -5034,7 +5038,7 @@
         <v>53.35</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="14" t="s">
         <v>6</v>
       </c>
@@ -5048,7 +5052,7 @@
         <v>16.39</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="12" t="s">
         <v>19</v>
       </c>
@@ -5060,7 +5064,7 @@
       </c>
       <c r="D223" s="13"/>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="14" t="s">
         <v>23</v>
       </c>
@@ -5074,7 +5078,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="12" t="s">
         <v>55</v>
       </c>
@@ -5088,7 +5092,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="14" t="s">
         <v>9</v>
       </c>
@@ -5102,7 +5106,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="12" t="s">
         <v>12</v>
       </c>
@@ -5116,7 +5120,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="14" t="s">
         <v>55</v>
       </c>
@@ -5130,7 +5134,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="12" t="s">
         <v>5</v>
       </c>
@@ -5144,7 +5148,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="14" t="s">
         <v>8</v>
       </c>
@@ -5158,7 +5162,7 @@
         <v>53.57</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="12" t="s">
         <v>6</v>
       </c>
@@ -5172,7 +5176,7 @@
         <v>16.46</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="14" t="s">
         <v>19</v>
       </c>
@@ -5184,7 +5188,7 @@
       </c>
       <c r="D232" s="15"/>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="12" t="s">
         <v>23</v>
       </c>
@@ -5198,7 +5202,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="14" t="s">
         <v>55</v>
       </c>
@@ -5212,7 +5216,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="12" t="s">
         <v>9</v>
       </c>
@@ -5226,7 +5230,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="14" t="s">
         <v>12</v>
       </c>
@@ -5240,7 +5244,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="12" t="s">
         <v>55</v>
       </c>
@@ -5254,7 +5258,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="14" t="s">
         <v>5</v>
       </c>
@@ -5268,7 +5272,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="12" t="s">
         <v>8</v>
       </c>
@@ -5282,7 +5286,7 @@
         <v>53.54</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="14" t="s">
         <v>6</v>
       </c>
@@ -5296,7 +5300,7 @@
         <v>16.559999999999999</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="12" t="s">
         <v>19</v>
       </c>
@@ -5308,7 +5312,7 @@
       </c>
       <c r="D241" s="13"/>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="14" t="s">
         <v>23</v>
       </c>
@@ -5322,7 +5326,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="12" t="s">
         <v>55</v>
       </c>
@@ -5336,7 +5340,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="14" t="s">
         <v>9</v>
       </c>
@@ -5350,7 +5354,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="12" t="s">
         <v>12</v>
       </c>
@@ -5364,7 +5368,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="14" t="s">
         <v>55</v>
       </c>
@@ -5378,7 +5382,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="12" t="s">
         <v>5</v>
       </c>
@@ -5392,7 +5396,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="14" t="s">
         <v>8</v>
       </c>
@@ -5406,7 +5410,7 @@
         <v>54.78</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="12" t="s">
         <v>6</v>
       </c>
@@ -5420,7 +5424,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="14" t="s">
         <v>19</v>
       </c>
@@ -5432,7 +5436,7 @@
       </c>
       <c r="D250" s="15"/>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="12" t="s">
         <v>23</v>
       </c>
@@ -5446,7 +5450,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="14" t="s">
         <v>55</v>
       </c>
@@ -5460,7 +5464,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="12" t="s">
         <v>9</v>
       </c>
@@ -5474,7 +5478,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="14" t="s">
         <v>12</v>
       </c>
@@ -5488,7 +5492,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="12" t="s">
         <v>55</v>
       </c>
@@ -5502,7 +5506,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="14" t="s">
         <v>5</v>
       </c>
@@ -5516,7 +5520,7 @@
         <v>8.35</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="12" t="s">
         <v>8</v>
       </c>
@@ -5530,7 +5534,7 @@
         <v>57.62</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="14" t="s">
         <v>6</v>
       </c>
@@ -5544,7 +5548,7 @@
         <v>16.79</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="12" t="s">
         <v>19</v>
       </c>
@@ -5556,7 +5560,7 @@
       </c>
       <c r="D259" s="13"/>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="14" t="s">
         <v>23</v>
       </c>
@@ -5570,7 +5574,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="12" t="s">
         <v>55</v>
       </c>
@@ -5584,7 +5588,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="14" t="s">
         <v>9</v>
       </c>
@@ -5598,7 +5602,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="12" t="s">
         <v>12</v>
       </c>
@@ -5612,7 +5616,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="14" t="s">
         <v>55</v>
       </c>
@@ -5626,7 +5630,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" s="12" t="s">
         <v>5</v>
       </c>
@@ -5640,7 +5644,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" s="14" t="s">
         <v>8</v>
       </c>
@@ -5654,7 +5658,7 @@
         <v>60.79</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" s="12" t="s">
         <v>6</v>
       </c>
@@ -5668,7 +5672,7 @@
         <v>17.04</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" s="14" t="s">
         <v>19</v>
       </c>
@@ -5680,7 +5684,7 @@
       </c>
       <c r="D268" s="15"/>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" s="12" t="s">
         <v>23</v>
       </c>
@@ -5694,7 +5698,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" s="14" t="s">
         <v>55</v>
       </c>
@@ -5708,7 +5712,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" s="12" t="s">
         <v>9</v>
       </c>
@@ -5722,7 +5726,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" s="14" t="s">
         <v>12</v>
       </c>
@@ -5736,7 +5740,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" s="12" t="s">
         <v>55</v>
       </c>
@@ -5750,7 +5754,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" s="14" t="s">
         <v>5</v>
       </c>
@@ -5764,7 +5768,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" s="12" t="s">
         <v>8</v>
       </c>
@@ -5778,7 +5782,7 @@
         <v>64.31</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" s="14" t="s">
         <v>6</v>
       </c>
@@ -5792,7 +5796,7 @@
         <v>17.11</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="12" t="s">
         <v>19</v>
       </c>
@@ -5804,7 +5808,7 @@
       </c>
       <c r="D277" s="13"/>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="14" t="s">
         <v>23</v>
       </c>
@@ -5818,7 +5822,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="12" t="s">
         <v>55</v>
       </c>
@@ -5832,7 +5836,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="14" t="s">
         <v>9</v>
       </c>
@@ -5846,7 +5850,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" s="12" t="s">
         <v>12</v>
       </c>
@@ -5860,7 +5864,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" s="14" t="s">
         <v>55</v>
       </c>
@@ -5874,7 +5878,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" s="12" t="s">
         <v>5</v>
       </c>
@@ -5888,7 +5892,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="14" t="s">
         <v>8</v>
       </c>
@@ -5902,7 +5906,7 @@
         <v>67.459999999999994</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" s="12" t="s">
         <v>6</v>
       </c>
@@ -5916,7 +5920,7 @@
         <v>17.16</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" s="14" t="s">
         <v>19</v>
       </c>
@@ -5928,7 +5932,7 @@
       </c>
       <c r="D286" s="15"/>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" s="12" t="s">
         <v>23</v>
       </c>
@@ -5942,7 +5946,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="14" t="s">
         <v>55</v>
       </c>
@@ -5956,7 +5960,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="12" t="s">
         <v>9</v>
       </c>
@@ -5970,7 +5974,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="14" t="s">
         <v>12</v>
       </c>
@@ -5984,7 +5988,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" s="12" t="s">
         <v>55</v>
       </c>
@@ -5998,7 +6002,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="14" t="s">
         <v>5</v>
       </c>
@@ -6012,7 +6016,7 @@
         <v>8.06</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" s="12" t="s">
         <v>8</v>
       </c>
@@ -6026,7 +6030,7 @@
         <v>70.95</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" s="14" t="s">
         <v>6</v>
       </c>
@@ -6040,7 +6044,7 @@
         <v>17.32</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" s="12" t="s">
         <v>19</v>
       </c>
@@ -6052,7 +6056,7 @@
       </c>
       <c r="D295" s="13"/>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" s="14" t="s">
         <v>23</v>
       </c>
@@ -6066,7 +6070,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" s="12" t="s">
         <v>55</v>
       </c>
@@ -6080,7 +6084,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" s="14" t="s">
         <v>9</v>
       </c>
@@ -6094,7 +6098,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" s="12" t="s">
         <v>12</v>
       </c>
@@ -6108,7 +6112,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" s="14" t="s">
         <v>55</v>
       </c>
@@ -6122,7 +6126,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" s="12" t="s">
         <v>5</v>
       </c>
@@ -6136,7 +6140,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" s="14" t="s">
         <v>8</v>
       </c>
@@ -6150,7 +6154,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" s="12" t="s">
         <v>6</v>
       </c>
@@ -6164,7 +6168,7 @@
         <v>17.41</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" s="14" t="s">
         <v>19</v>
       </c>
@@ -6176,7 +6180,7 @@
       </c>
       <c r="D304" s="15"/>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" s="12" t="s">
         <v>23</v>
       </c>
@@ -6190,7 +6194,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" s="14" t="s">
         <v>55</v>
       </c>
@@ -6204,7 +6208,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" s="12" t="s">
         <v>9</v>
       </c>
@@ -6218,7 +6222,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" s="14" t="s">
         <v>12</v>
       </c>
@@ -6232,7 +6236,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" s="12" t="s">
         <v>55</v>
       </c>
@@ -6246,7 +6250,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" s="14" t="s">
         <v>5</v>
       </c>
@@ -6260,7 +6264,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" s="12" t="s">
         <v>8</v>
       </c>
@@ -6274,7 +6278,7 @@
         <v>72.459999999999994</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" s="14" t="s">
         <v>6</v>
       </c>
@@ -6288,7 +6292,7 @@
         <v>17.559999999999999</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" s="12" t="s">
         <v>19</v>
       </c>
@@ -6300,7 +6304,7 @@
       </c>
       <c r="D313" s="13"/>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" s="14" t="s">
         <v>23</v>
       </c>
@@ -6314,7 +6318,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" s="12" t="s">
         <v>55</v>
       </c>
@@ -6328,7 +6332,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" s="14" t="s">
         <v>9</v>
       </c>
@@ -6342,7 +6346,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" s="12" t="s">
         <v>12</v>
       </c>
@@ -6356,7 +6360,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" s="14" t="s">
         <v>55</v>
       </c>
@@ -6370,7 +6374,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" s="12" t="s">
         <v>5</v>
       </c>
@@ -6384,7 +6388,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" s="14" t="s">
         <v>8</v>
       </c>
@@ -6398,7 +6402,7 @@
         <v>73.33</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" s="12" t="s">
         <v>6</v>
       </c>
@@ -6412,7 +6416,7 @@
         <v>17.78</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" s="14" t="s">
         <v>19</v>
       </c>
@@ -6424,7 +6428,7 @@
       </c>
       <c r="D322" s="15"/>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" s="12" t="s">
         <v>23</v>
       </c>
@@ -6438,7 +6442,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" s="14" t="s">
         <v>55</v>
       </c>
@@ -6452,7 +6456,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" s="12" t="s">
         <v>9</v>
       </c>
@@ -6466,7 +6470,7 @@
         <v>13.14</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" s="14" t="s">
         <v>12</v>
       </c>
@@ -6480,7 +6484,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" s="12" t="s">
         <v>55</v>
       </c>
@@ -6494,7 +6498,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" s="14" t="s">
         <v>5</v>
       </c>
@@ -6508,7 +6512,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" s="12" t="s">
         <v>8</v>
       </c>
@@ -6522,7 +6526,7 @@
         <v>73.22</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" s="14" t="s">
         <v>6</v>
       </c>
@@ -6536,7 +6540,7 @@
         <v>17.920000000000002</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" s="12" t="s">
         <v>19</v>
       </c>
@@ -6548,7 +6552,7 @@
       </c>
       <c r="D331" s="13"/>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" s="14" t="s">
         <v>23</v>
       </c>
@@ -6562,7 +6566,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" s="12" t="s">
         <v>55</v>
       </c>
@@ -6576,7 +6580,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" s="14" t="s">
         <v>9</v>
       </c>
@@ -6590,7 +6594,7 @@
         <v>16.79</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" s="12" t="s">
         <v>12</v>
       </c>
@@ -6604,7 +6608,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" s="14" t="s">
         <v>55</v>
       </c>
@@ -6618,7 +6622,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" s="12" t="s">
         <v>5</v>
       </c>
@@ -6632,7 +6636,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" s="14" t="s">
         <v>8</v>
       </c>
@@ -6646,7 +6650,7 @@
         <v>70.95</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" s="12" t="s">
         <v>6</v>
       </c>
@@ -6660,7 +6664,7 @@
         <v>18.05</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" s="14" t="s">
         <v>19</v>
       </c>
@@ -6672,7 +6676,7 @@
       </c>
       <c r="D340" s="15"/>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" s="12" t="s">
         <v>23</v>
       </c>
@@ -6686,7 +6690,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" s="14" t="s">
         <v>55</v>
       </c>
@@ -6700,7 +6704,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" s="12" t="s">
         <v>9</v>
       </c>
@@ -6714,7 +6718,7 @@
         <v>18.190000000000001</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" s="14" t="s">
         <v>12</v>
       </c>
@@ -6728,7 +6732,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" s="12" t="s">
         <v>55</v>
       </c>
@@ -6742,7 +6746,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" s="14" t="s">
         <v>5</v>
       </c>
@@ -6756,7 +6760,7 @@
         <v>9.83</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" s="12" t="s">
         <v>8</v>
       </c>
@@ -6770,7 +6774,7 @@
         <v>67.48</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" s="14" t="s">
         <v>6</v>
       </c>
@@ -6784,7 +6788,7 @@
         <v>18.12</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" s="12" t="s">
         <v>19</v>
       </c>
@@ -6796,7 +6800,7 @@
       </c>
       <c r="D349" s="13"/>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" s="14" t="s">
         <v>23</v>
       </c>
@@ -6810,7 +6814,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" s="12" t="s">
         <v>55</v>
       </c>
@@ -6824,7 +6828,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" s="14" t="s">
         <v>9</v>
       </c>
@@ -6838,7 +6842,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" s="12" t="s">
         <v>12</v>
       </c>
@@ -6852,7 +6856,7 @@
         <v>8.68</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" s="14" t="s">
         <v>55</v>
       </c>
@@ -6866,7 +6870,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" s="12" t="s">
         <v>5</v>
       </c>
@@ -6880,7 +6884,7 @@
         <v>9.69</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" s="14" t="s">
         <v>8</v>
       </c>
@@ -6894,7 +6898,7 @@
         <v>61.81</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" s="12" t="s">
         <v>6</v>
       </c>
@@ -6908,7 +6912,7 @@
         <v>18.239999999999998</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" s="14" t="s">
         <v>19</v>
       </c>
@@ -6920,7 +6924,7 @@
       </c>
       <c r="D358" s="15"/>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" s="12" t="s">
         <v>23</v>
       </c>
@@ -6934,7 +6938,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" s="14" t="s">
         <v>55</v>
       </c>
@@ -6948,7 +6952,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" s="12" t="s">
         <v>9</v>
       </c>
@@ -6962,7 +6966,7 @@
         <v>18.91</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" s="14" t="s">
         <v>12</v>
       </c>
@@ -6976,7 +6980,7 @@
         <v>9.14</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" s="12" t="s">
         <v>55</v>
       </c>
@@ -6990,7 +6994,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" s="14" t="s">
         <v>5</v>
       </c>
@@ -7004,7 +7008,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" s="12" t="s">
         <v>8</v>
       </c>
@@ -7018,7 +7022,7 @@
         <v>58.22</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" s="14" t="s">
         <v>6</v>
       </c>
@@ -7032,7 +7036,7 @@
         <v>18.32</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="12" t="s">
         <v>19</v>
       </c>
@@ -7044,7 +7048,7 @@
       </c>
       <c r="D367" s="13"/>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" s="14" t="s">
         <v>23</v>
       </c>
@@ -7058,7 +7062,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" s="12" t="s">
         <v>55</v>
       </c>
@@ -7072,7 +7076,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" s="14" t="s">
         <v>9</v>
       </c>
@@ -7086,7 +7090,7 @@
         <v>19.29</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" s="12" t="s">
         <v>12</v>
       </c>
@@ -7100,7 +7104,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" s="14" t="s">
         <v>55</v>
       </c>
@@ -7114,7 +7118,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" s="12" t="s">
         <v>5</v>
       </c>
@@ -7128,7 +7132,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" s="14" t="s">
         <v>8</v>
       </c>
@@ -7142,7 +7146,7 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" s="12" t="s">
         <v>6</v>
       </c>
@@ -7156,7 +7160,7 @@
         <v>18.489999999999998</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" s="14" t="s">
         <v>19</v>
       </c>
@@ -7168,7 +7172,7 @@
       </c>
       <c r="D376" s="15"/>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" s="12" t="s">
         <v>23</v>
       </c>
@@ -7182,7 +7186,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" s="14" t="s">
         <v>55</v>
       </c>
@@ -7196,7 +7200,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" s="12" t="s">
         <v>9</v>
       </c>
@@ -7210,7 +7214,7 @@
         <v>19.690000000000001</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" s="14" t="s">
         <v>12</v>
       </c>
@@ -7224,7 +7228,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" s="12" t="s">
         <v>55</v>
       </c>
@@ -7238,7 +7242,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" s="14" t="s">
         <v>5</v>
       </c>
@@ -7252,7 +7256,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" s="12" t="s">
         <v>8</v>
       </c>
@@ -7266,7 +7270,7 @@
         <v>57.35</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" s="14" t="s">
         <v>6</v>
       </c>
@@ -7280,7 +7284,7 @@
         <v>18.559999999999999</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" s="12" t="s">
         <v>19</v>
       </c>
@@ -7292,7 +7296,7 @@
       </c>
       <c r="D385" s="13"/>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" s="14" t="s">
         <v>23</v>
       </c>
@@ -7306,7 +7310,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" s="12" t="s">
         <v>55</v>
       </c>
@@ -7320,7 +7324,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" s="14" t="s">
         <v>9</v>
       </c>
@@ -7334,7 +7338,7 @@
         <v>20.11</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" s="12" t="s">
         <v>12</v>
       </c>
@@ -7348,7 +7352,7 @@
         <v>10.23</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" s="14" t="s">
         <v>55</v>
       </c>
@@ -7362,7 +7366,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" s="12" t="s">
         <v>5</v>
       </c>
@@ -7376,7 +7380,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" s="14" t="s">
         <v>8</v>
       </c>
@@ -7390,7 +7394,7 @@
         <v>57.41</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" s="12" t="s">
         <v>6</v>
       </c>
@@ -7404,7 +7408,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" s="14" t="s">
         <v>19</v>
       </c>
@@ -7416,7 +7420,7 @@
       </c>
       <c r="D394" s="15"/>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" s="12" t="s">
         <v>23</v>
       </c>
@@ -7430,7 +7434,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" s="14" t="s">
         <v>55</v>
       </c>
@@ -7444,7 +7448,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" s="12" t="s">
         <v>9</v>
       </c>
@@ -7458,7 +7462,7 @@
         <v>20.87</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" s="14" t="s">
         <v>12</v>
       </c>
@@ -7472,7 +7476,7 @@
         <v>10.68</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" s="12" t="s">
         <v>55</v>
       </c>
@@ -7486,7 +7490,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" s="14" t="s">
         <v>5</v>
       </c>
@@ -7500,7 +7504,7 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" s="12" t="s">
         <v>8</v>
       </c>
@@ -7514,7 +7518,7 @@
         <v>56.24</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" s="14" t="s">
         <v>6</v>
       </c>
@@ -7528,7 +7532,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" s="12" t="s">
         <v>19</v>
       </c>
@@ -7540,7 +7544,7 @@
       </c>
       <c r="D403" s="13"/>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" s="14" t="s">
         <v>23</v>
       </c>
@@ -7554,7 +7558,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" s="12" t="s">
         <v>55</v>
       </c>
@@ -7568,7 +7572,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="14" t="s">
         <v>9</v>
       </c>
@@ -7582,7 +7586,7 @@
         <v>21.66</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="12" t="s">
         <v>12</v>
       </c>
@@ -7596,7 +7600,7 @@
         <v>10.87</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" s="14" t="s">
         <v>55</v>
       </c>
@@ -7610,7 +7614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" s="12" t="s">
         <v>5</v>
       </c>
@@ -7624,7 +7628,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" s="14" t="s">
         <v>8</v>
       </c>
@@ -7638,7 +7642,7 @@
         <v>55.63</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" s="12" t="s">
         <v>6</v>
       </c>
@@ -7652,7 +7656,7 @@
         <v>18.809999999999999</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" s="14" t="s">
         <v>19</v>
       </c>
@@ -7664,7 +7668,7 @@
       </c>
       <c r="D412" s="15"/>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" s="12" t="s">
         <v>23</v>
       </c>
@@ -7678,7 +7682,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" s="14" t="s">
         <v>55</v>
       </c>
@@ -7692,7 +7696,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" s="12" t="s">
         <v>9</v>
       </c>
@@ -7706,7 +7710,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" s="14" t="s">
         <v>12</v>
       </c>
@@ -7720,7 +7724,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A417" s="12" t="s">
         <v>55</v>
       </c>
@@ -7734,7 +7738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A418" s="14" t="s">
         <v>5</v>
       </c>
@@ -7748,7 +7752,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A419" s="12" t="s">
         <v>8</v>
       </c>
@@ -7762,7 +7766,7 @@
         <v>56.32</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A420" s="14" t="s">
         <v>6</v>
       </c>
@@ -7776,7 +7780,7 @@
         <v>18.93</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A421" s="12" t="s">
         <v>19</v>
       </c>
@@ -7788,7 +7792,7 @@
       </c>
       <c r="D421" s="13"/>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A422" s="14" t="s">
         <v>23</v>
       </c>
@@ -7802,7 +7806,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A423" s="12" t="s">
         <v>55</v>
       </c>
@@ -7816,7 +7820,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A424" s="14" t="s">
         <v>9</v>
       </c>
@@ -7830,7 +7834,7 @@
         <v>24.56</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A425" s="12" t="s">
         <v>12</v>
       </c>
@@ -7844,7 +7848,7 @@
         <v>11.82</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" s="14" t="s">
         <v>55</v>
       </c>
@@ -7858,7 +7862,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" s="12" t="s">
         <v>5</v>
       </c>
@@ -7872,7 +7876,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" s="14" t="s">
         <v>8</v>
       </c>
@@ -7886,7 +7890,7 @@
         <v>57.28</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" s="12" t="s">
         <v>6</v>
       </c>
@@ -7900,7 +7904,7 @@
         <v>18.850000000000001</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" s="14" t="s">
         <v>19</v>
       </c>
@@ -7912,7 +7916,7 @@
       </c>
       <c r="D430" s="15"/>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A431" s="12" t="s">
         <v>23</v>
       </c>
@@ -7926,7 +7930,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A432" s="14" t="s">
         <v>55</v>
       </c>
@@ -7940,7 +7944,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A433" s="12" t="s">
         <v>9</v>
       </c>
@@ -7954,7 +7958,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A434" s="14" t="s">
         <v>12</v>
       </c>
@@ -7968,7 +7972,7 @@
         <v>12.31</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A435" s="12" t="s">
         <v>55</v>
       </c>
@@ -7982,7 +7986,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" s="14" t="s">
         <v>5</v>
       </c>
@@ -7996,7 +8000,7 @@
         <v>24.64</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A437" s="12" t="s">
         <v>8</v>
       </c>
@@ -8010,7 +8014,7 @@
         <v>49.08</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A438" s="14" t="s">
         <v>6</v>
       </c>
@@ -8024,7 +8028,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A439" s="12" t="s">
         <v>19</v>
       </c>
@@ -8038,7 +8042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A440" s="14" t="s">
         <v>23</v>
       </c>
@@ -8052,7 +8056,7 @@
         <v>60.16</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A441" s="12" t="s">
         <v>55</v>
       </c>
@@ -8066,7 +8070,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" s="14" t="s">
         <v>9</v>
       </c>
@@ -8080,7 +8084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" s="12" t="s">
         <v>12</v>
       </c>
@@ -8094,7 +8098,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A444" s="14" t="s">
         <v>55</v>
       </c>
@@ -8108,7 +8112,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" s="12" t="s">
         <v>5</v>
       </c>
@@ -8122,7 +8126,7 @@
         <v>29.74</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A446" s="14" t="s">
         <v>8</v>
       </c>
@@ -8136,7 +8140,7 @@
         <v>50.45</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A447" s="12" t="s">
         <v>6</v>
       </c>
@@ -8150,7 +8154,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A448" s="14" t="s">
         <v>19</v>
       </c>
@@ -8164,7 +8168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A449" s="12" t="s">
         <v>23</v>
       </c>
@@ -8178,7 +8182,7 @@
         <v>53.71</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A450" s="14" t="s">
         <v>55</v>
       </c>
@@ -8192,7 +8196,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A451" s="12" t="s">
         <v>9</v>
       </c>
@@ -8206,7 +8210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A452" s="14" t="s">
         <v>12</v>
       </c>
@@ -8220,7 +8224,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A453" s="12" t="s">
         <v>55</v>
       </c>
@@ -8234,7 +8238,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A454" s="14" t="s">
         <v>5</v>
       </c>
@@ -8248,7 +8252,7 @@
         <v>33.22</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A455" s="12" t="s">
         <v>8</v>
       </c>
@@ -8262,7 +8266,7 @@
         <v>48.13</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A456" s="14" t="s">
         <v>6</v>
       </c>
@@ -8276,7 +8280,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A457" s="12" t="s">
         <v>19</v>
       </c>
@@ -8290,7 +8294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A458" s="14" t="s">
         <v>23</v>
       </c>
@@ -8304,7 +8308,7 @@
         <v>62.09</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A459" s="12" t="s">
         <v>55</v>
       </c>
@@ -8318,7 +8322,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A460" s="14" t="s">
         <v>9</v>
       </c>
@@ -8332,7 +8336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A461" s="12" t="s">
         <v>12</v>
       </c>
@@ -8346,7 +8350,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A462" s="14" t="s">
         <v>55</v>
       </c>
@@ -8360,7 +8364,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A463" s="12" t="s">
         <v>5</v>
       </c>
@@ -8374,7 +8378,7 @@
         <v>36.369999999999997</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A464" s="14" t="s">
         <v>8</v>
       </c>
@@ -8388,7 +8392,7 @@
         <v>56.79</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A465" s="12" t="s">
         <v>6</v>
       </c>
@@ -8402,7 +8406,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A466" s="14" t="s">
         <v>19</v>
       </c>
@@ -8416,7 +8420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A467" s="12" t="s">
         <v>23</v>
       </c>
@@ -8430,7 +8434,7 @@
         <v>54.81</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A468" s="14" t="s">
         <v>55</v>
       </c>
@@ -8444,7 +8448,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A469" s="12" t="s">
         <v>9</v>
       </c>
@@ -8458,7 +8462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A470" s="14" t="s">
         <v>12</v>
       </c>
@@ -8472,7 +8476,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A471" s="12" t="s">
         <v>55</v>
       </c>
@@ -8486,7 +8490,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A472" s="14" t="s">
         <v>5</v>
       </c>
@@ -8500,7 +8504,7 @@
         <v>42.65</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A473" s="12" t="s">
         <v>8</v>
       </c>
@@ -8514,7 +8518,7 @@
         <v>62.86</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A474" s="14" t="s">
         <v>6</v>
       </c>
@@ -8528,7 +8532,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A475" s="12" t="s">
         <v>19</v>
       </c>
@@ -8542,7 +8546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A476" s="14" t="s">
         <v>23</v>
       </c>
@@ -8556,7 +8560,7 @@
         <v>42.43</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A477" s="12" t="s">
         <v>55</v>
       </c>
@@ -8570,7 +8574,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A478" s="14" t="s">
         <v>9</v>
       </c>
@@ -8584,7 +8588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A479" s="12" t="s">
         <v>12</v>
       </c>
@@ -8598,7 +8602,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A480" s="14" t="s">
         <v>55</v>
       </c>
@@ -8612,7 +8616,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A481" s="12" t="s">
         <v>5</v>
       </c>
@@ -8626,7 +8630,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A482" s="14" t="s">
         <v>8</v>
       </c>
@@ -8640,7 +8644,7 @@
         <v>72.3</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A483" s="12" t="s">
         <v>6</v>
       </c>
@@ -8654,7 +8658,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A484" s="14" t="s">
         <v>19</v>
       </c>
@@ -8668,7 +8672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A485" s="12" t="s">
         <v>23</v>
       </c>
@@ -8682,7 +8686,7 @@
         <v>35.049999999999997</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A486" s="14" t="s">
         <v>55</v>
       </c>
@@ -8696,7 +8700,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A487" s="12" t="s">
         <v>9</v>
       </c>
@@ -8710,7 +8714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A488" s="14" t="s">
         <v>12</v>
       </c>
@@ -8724,7 +8728,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A489" s="12" t="s">
         <v>55</v>
       </c>
@@ -8738,7 +8742,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A490" s="14" t="s">
         <v>5</v>
       </c>
@@ -8752,7 +8756,7 @@
         <v>41.45</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A491" s="12" t="s">
         <v>8</v>
       </c>
@@ -8766,7 +8770,7 @@
         <v>76.569999999999993</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A492" s="14" t="s">
         <v>6</v>
       </c>
@@ -8780,7 +8784,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A493" s="12" t="s">
         <v>19</v>
       </c>
@@ -8794,7 +8798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A494" s="14" t="s">
         <v>23</v>
       </c>
@@ -8808,7 +8812,7 @@
         <v>34.619999999999997</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A495" s="12" t="s">
         <v>55</v>
       </c>
@@ -8822,7 +8826,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A496" s="14" t="s">
         <v>9</v>
       </c>
@@ -8836,7 +8840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A497" s="12" t="s">
         <v>12</v>
       </c>
@@ -8850,7 +8854,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A498" s="14" t="s">
         <v>55</v>
       </c>
@@ -8864,7 +8868,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A499" s="12" t="s">
         <v>5</v>
       </c>
@@ -8878,7 +8882,7 @@
         <v>41.35</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A500" s="14" t="s">
         <v>8</v>
       </c>
@@ -8892,7 +8896,7 @@
         <v>83.62</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A501" s="12" t="s">
         <v>6</v>
       </c>
@@ -8906,7 +8910,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A502" s="14" t="s">
         <v>19</v>
       </c>
@@ -8920,7 +8924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A503" s="12" t="s">
         <v>23</v>
       </c>
@@ -8934,7 +8938,7 @@
         <v>27.39</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A504" s="14" t="s">
         <v>55</v>
       </c>
@@ -8948,7 +8952,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A505" s="12" t="s">
         <v>9</v>
       </c>
@@ -8962,7 +8966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A506" s="14" t="s">
         <v>12</v>
       </c>
@@ -8976,7 +8980,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A507" s="12" t="s">
         <v>55</v>
       </c>
@@ -8990,7 +8994,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A508" s="14" t="s">
         <v>5</v>
       </c>
@@ -9004,7 +9008,7 @@
         <v>40.340000000000003</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A509" s="12" t="s">
         <v>8</v>
       </c>
@@ -9018,7 +9022,7 @@
         <v>83.65</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A510" s="14" t="s">
         <v>6</v>
       </c>
@@ -9032,7 +9036,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A511" s="12" t="s">
         <v>19</v>
       </c>
@@ -9046,7 +9050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A512" s="14" t="s">
         <v>23</v>
       </c>
@@ -9060,7 +9064,7 @@
         <v>24.72</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A513" s="12" t="s">
         <v>55</v>
       </c>
@@ -9074,7 +9078,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A514" s="14" t="s">
         <v>9</v>
       </c>
@@ -9088,7 +9092,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A515" s="12" t="s">
         <v>12</v>
       </c>
@@ -9102,7 +9106,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A516" s="14" t="s">
         <v>55</v>
       </c>
@@ -9116,7 +9120,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A517" s="12" t="s">
         <v>5</v>
       </c>
@@ -9130,7 +9134,7 @@
         <v>37.119999999999997</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A518" s="14" t="s">
         <v>8</v>
       </c>
@@ -9144,7 +9148,7 @@
         <v>71.349999999999994</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A519" s="12" t="s">
         <v>6</v>
       </c>
@@ -9158,7 +9162,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A520" s="14" t="s">
         <v>19</v>
       </c>
@@ -9172,7 +9176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A521" s="12" t="s">
         <v>23</v>
       </c>
@@ -9186,7 +9190,7 @@
         <v>19.739999999999998</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A522" s="14" t="s">
         <v>55</v>
       </c>
@@ -9200,7 +9204,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A523" s="12" t="s">
         <v>9</v>
       </c>
@@ -9214,7 +9218,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A524" s="14" t="s">
         <v>12</v>
       </c>
@@ -9228,7 +9232,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A525" s="12" t="s">
         <v>55</v>
       </c>
@@ -9242,7 +9246,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A526" s="14" t="s">
         <v>5</v>
       </c>
@@ -9256,7 +9260,7 @@
         <v>36.94</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A527" s="12" t="s">
         <v>8</v>
       </c>
@@ -9270,7 +9274,7 @@
         <v>73.989999999999995</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A528" s="14" t="s">
         <v>6</v>
       </c>
@@ -9284,7 +9288,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A529" s="12" t="s">
         <v>19</v>
       </c>
@@ -9298,7 +9302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A530" s="14" t="s">
         <v>23</v>
       </c>
@@ -9312,7 +9316,7 @@
         <v>17.84</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A531" s="12" t="s">
         <v>55</v>
       </c>
@@ -9326,7 +9330,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A532" s="14" t="s">
         <v>9</v>
       </c>
@@ -9340,7 +9344,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A533" s="12" t="s">
         <v>12</v>
       </c>
@@ -9354,7 +9358,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A534" s="14" t="s">
         <v>55</v>
       </c>
@@ -9368,7 +9372,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A535" s="12" t="s">
         <v>5</v>
       </c>
@@ -9382,7 +9386,7 @@
         <v>41.48</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A536" s="14" t="s">
         <v>8</v>
       </c>
@@ -9396,7 +9400,7 @@
         <v>70.010000000000005</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A537" s="12" t="s">
         <v>6</v>
       </c>
@@ -9410,7 +9414,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A538" s="14" t="s">
         <v>19</v>
       </c>
@@ -9424,7 +9428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A539" s="12" t="s">
         <v>23</v>
       </c>
@@ -9438,7 +9442,7 @@
         <v>17.170000000000002</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A540" s="14" t="s">
         <v>55</v>
       </c>
@@ -9452,7 +9456,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A541" s="12" t="s">
         <v>9</v>
       </c>
@@ -9466,7 +9470,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A542" s="14" t="s">
         <v>12</v>
       </c>
@@ -9480,7 +9484,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A543" s="12" t="s">
         <v>55</v>
       </c>
@@ -9494,7 +9498,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A544" s="14" t="s">
         <v>5</v>
       </c>
@@ -9508,7 +9512,7 @@
         <v>45.57</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A545" s="12" t="s">
         <v>8</v>
       </c>
@@ -9522,7 +9526,7 @@
         <v>62.53</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A546" s="14" t="s">
         <v>6</v>
       </c>
@@ -9536,7 +9540,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A547" s="12" t="s">
         <v>19</v>
       </c>
@@ -9550,7 +9554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A548" s="14" t="s">
         <v>23</v>
       </c>
@@ -9564,7 +9568,7 @@
         <v>16.29</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A549" s="12" t="s">
         <v>55</v>
       </c>
@@ -9578,7 +9582,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A550" s="14" t="s">
         <v>9</v>
       </c>
@@ -9592,7 +9596,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A551" s="12" t="s">
         <v>12</v>
       </c>
@@ -9606,7 +9610,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A552" s="14" t="s">
         <v>55</v>
       </c>
@@ -9620,7 +9624,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A553" s="12" t="s">
         <v>5</v>
       </c>
@@ -9634,7 +9638,7 @@
         <v>41.82</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A554" s="14" t="s">
         <v>8</v>
       </c>
@@ -9648,7 +9652,7 @@
         <v>52.73</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A555" s="12" t="s">
         <v>6</v>
       </c>
@@ -9662,7 +9666,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A556" s="14" t="s">
         <v>19</v>
       </c>
@@ -9676,7 +9680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A557" s="12" t="s">
         <v>23</v>
       </c>
@@ -9690,7 +9694,7 @@
         <v>13.17</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A558" s="14" t="s">
         <v>55</v>
       </c>
@@ -9704,7 +9708,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A559" s="12" t="s">
         <v>9</v>
       </c>
@@ -9718,7 +9722,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A560" s="14" t="s">
         <v>12</v>
       </c>
@@ -9732,7 +9736,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A561" s="12" t="s">
         <v>55</v>
       </c>
@@ -9746,7 +9750,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A562" s="14" t="s">
         <v>5</v>
       </c>
@@ -9760,7 +9764,7 @@
         <v>40.28</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A563" s="12" t="s">
         <v>8</v>
       </c>
@@ -9774,7 +9778,7 @@
         <v>45.35</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A564" s="14" t="s">
         <v>6</v>
       </c>
@@ -9788,7 +9792,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A565" s="12" t="s">
         <v>19</v>
       </c>
@@ -9802,7 +9806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A566" s="14" t="s">
         <v>23</v>
       </c>
@@ -9816,7 +9820,7 @@
         <v>12.33</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A567" s="12" t="s">
         <v>55</v>
       </c>
@@ -9830,7 +9834,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A568" s="14" t="s">
         <v>9</v>
       </c>
@@ -9844,7 +9848,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A569" s="12" t="s">
         <v>12</v>
       </c>
@@ -9858,7 +9862,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A570" s="14" t="s">
         <v>55</v>
       </c>
@@ -9872,7 +9876,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A571" s="12" t="s">
         <v>5</v>
       </c>
@@ -9886,7 +9890,7 @@
         <v>40.03</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A572" s="14" t="s">
         <v>8</v>
       </c>
@@ -9900,7 +9904,7 @@
         <v>53.68</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A573" s="12" t="s">
         <v>6</v>
       </c>
@@ -9914,7 +9918,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A574" s="14" t="s">
         <v>19</v>
       </c>
@@ -9928,7 +9932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A575" s="12" t="s">
         <v>23</v>
       </c>
@@ -9942,7 +9946,7 @@
         <v>11.01</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A576" s="14" t="s">
         <v>55</v>
       </c>
@@ -9956,7 +9960,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A577" s="12" t="s">
         <v>9</v>
       </c>
@@ -9970,7 +9974,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A578" s="14" t="s">
         <v>12</v>
       </c>
@@ -9984,7 +9988,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A579" s="12" t="s">
         <v>55</v>
       </c>
@@ -9998,7 +10002,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A580" s="14" t="s">
         <v>5</v>
       </c>
@@ -10012,7 +10016,7 @@
         <v>32.92</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A581" s="12" t="s">
         <v>8</v>
       </c>
@@ -10026,7 +10030,7 @@
         <v>61.09</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A582" s="14" t="s">
         <v>6</v>
       </c>
@@ -10040,7 +10044,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A583" s="12" t="s">
         <v>19</v>
       </c>
@@ -10054,7 +10058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A584" s="14" t="s">
         <v>23</v>
       </c>
@@ -10068,7 +10072,7 @@
         <v>10.63</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A585" s="12" t="s">
         <v>55</v>
       </c>
@@ -10082,7 +10086,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A586" s="14" t="s">
         <v>9</v>
       </c>
@@ -10096,7 +10100,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A587" s="12" t="s">
         <v>12</v>
       </c>
@@ -10110,7 +10114,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A588" s="14" t="s">
         <v>55</v>
       </c>
@@ -10124,7 +10128,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A589" s="12" t="s">
         <v>5</v>
       </c>
@@ -10138,7 +10142,7 @@
         <v>30.09</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A590" s="14" t="s">
         <v>8</v>
       </c>
@@ -10152,7 +10156,7 @@
         <v>67.959999999999994</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A591" s="12" t="s">
         <v>6</v>
       </c>
@@ -10166,7 +10170,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A592" s="14" t="s">
         <v>19</v>
       </c>
@@ -10180,7 +10184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A593" s="12" t="s">
         <v>23</v>
       </c>
@@ -10194,7 +10198,7 @@
         <v>10.01</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A594" s="14" t="s">
         <v>55</v>
       </c>
@@ -10208,7 +10212,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A595" s="12" t="s">
         <v>9</v>
       </c>
@@ -10222,7 +10226,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A596" s="14" t="s">
         <v>12</v>
       </c>
@@ -10236,7 +10240,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A597" s="12" t="s">
         <v>55</v>
       </c>
@@ -10250,7 +10254,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A598" s="14" t="s">
         <v>5</v>
       </c>
@@ -10264,7 +10268,7 @@
         <v>26.24</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A599" s="12" t="s">
         <v>8</v>
       </c>
@@ -10278,7 +10282,7 @@
         <v>62.24</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A600" s="14" t="s">
         <v>6</v>
       </c>
@@ -10292,7 +10296,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A601" s="12" t="s">
         <v>19</v>
       </c>
@@ -10306,7 +10310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A602" s="14" t="s">
         <v>23</v>
       </c>
@@ -10320,7 +10324,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A603" s="12" t="s">
         <v>55</v>
       </c>
@@ -10334,7 +10338,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A604" s="14" t="s">
         <v>9</v>
       </c>
@@ -10348,7 +10352,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" s="12" t="s">
         <v>12</v>
       </c>
@@ -10362,7 +10366,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" s="14" t="s">
         <v>55</v>
       </c>
@@ -10376,7 +10380,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A607" s="12" t="s">
         <v>5</v>
       </c>
@@ -10390,7 +10394,7 @@
         <v>17.36</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A608" s="14" t="s">
         <v>8</v>
       </c>
@@ -10404,7 +10408,7 @@
         <v>68.61</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A609" s="12" t="s">
         <v>6</v>
       </c>
@@ -10418,7 +10422,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A610" s="14" t="s">
         <v>19</v>
       </c>
@@ -10432,7 +10436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A611" s="12" t="s">
         <v>23</v>
       </c>
@@ -10446,7 +10450,7 @@
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A612" s="14" t="s">
         <v>55</v>
       </c>
@@ -10460,7 +10464,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A613" s="12" t="s">
         <v>9</v>
       </c>
@@ -10474,7 +10478,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A614" s="14" t="s">
         <v>12</v>
       </c>
@@ -10488,7 +10492,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A615" s="12" t="s">
         <v>55</v>
       </c>
@@ -10502,7 +10506,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A616" s="14" t="s">
         <v>5</v>
       </c>
@@ -10516,7 +10520,7 @@
         <v>12.34</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A617" s="12" t="s">
         <v>8</v>
       </c>
@@ -10530,7 +10534,7 @@
         <v>64.73</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A618" s="14" t="s">
         <v>6</v>
       </c>
@@ -10544,7 +10548,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A619" s="12" t="s">
         <v>19</v>
       </c>
@@ -10558,7 +10562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A620" s="14" t="s">
         <v>23</v>
       </c>
@@ -10572,7 +10576,7 @@
         <v>8.44</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A621" s="12" t="s">
         <v>55</v>
       </c>
@@ -10586,7 +10590,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A622" s="14" t="s">
         <v>9</v>
       </c>
@@ -10600,7 +10604,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A623" s="12" t="s">
         <v>12</v>
       </c>
@@ -10614,7 +10618,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A624" s="14" t="s">
         <v>55</v>
       </c>
@@ -10628,7 +10632,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A625" s="12" t="s">
         <v>5</v>
       </c>
@@ -10642,7 +10646,7 @@
         <v>12.94</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A626" s="14" t="s">
         <v>8</v>
       </c>
@@ -10656,7 +10660,7 @@
         <v>69.73</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A627" s="12" t="s">
         <v>6</v>
       </c>
@@ -10670,7 +10674,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A628" s="14" t="s">
         <v>19</v>
       </c>
@@ -10684,7 +10688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A629" s="12" t="s">
         <v>23</v>
       </c>
@@ -10698,7 +10702,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" s="14" t="s">
         <v>55</v>
       </c>
@@ -10712,7 +10716,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A631" s="12" t="s">
         <v>9</v>
       </c>
@@ -10726,7 +10730,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A632" s="14" t="s">
         <v>12</v>
       </c>
@@ -10740,7 +10744,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A633" s="12" t="s">
         <v>55</v>
       </c>
@@ -10754,7 +10758,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A634" s="14" t="s">
         <v>5</v>
       </c>
@@ -10768,7 +10772,7 @@
         <v>20.88</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A635" s="12" t="s">
         <v>8</v>
       </c>
@@ -10782,7 +10786,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A636" s="14" t="s">
         <v>6</v>
       </c>
@@ -10796,7 +10800,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A637" s="12" t="s">
         <v>19</v>
       </c>
@@ -10810,7 +10814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A638" s="14" t="s">
         <v>23</v>
       </c>
@@ -10824,7 +10828,7 @@
         <v>10.28</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A639" s="12" t="s">
         <v>55</v>
       </c>
@@ -10838,7 +10842,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A640" s="14" t="s">
         <v>9</v>
       </c>
@@ -10852,7 +10856,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A641" s="12" t="s">
         <v>12</v>
       </c>
@@ -10866,7 +10870,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A642" s="14" t="s">
         <v>55</v>
       </c>
@@ -10880,7 +10884,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A643" s="12" t="s">
         <v>5</v>
       </c>
@@ -10894,7 +10898,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A644" s="14" t="s">
         <v>8</v>
       </c>
@@ -10908,7 +10912,7 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A645" s="12" t="s">
         <v>6</v>
       </c>
@@ -10922,7 +10926,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A646" s="14" t="s">
         <v>19</v>
       </c>
@@ -10936,7 +10940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A647" s="12" t="s">
         <v>23</v>
       </c>
@@ -10950,7 +10954,7 @@
         <v>10.23</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A648" s="14" t="s">
         <v>55</v>
       </c>
@@ -10964,7 +10968,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A649" s="12" t="s">
         <v>9</v>
       </c>
@@ -10978,7 +10982,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A650" s="14" t="s">
         <v>12</v>
       </c>
@@ -10992,7 +10996,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A651" s="12" t="s">
         <v>63</v>
       </c>
@@ -11006,7 +11010,7 @@
         <v>44.35</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A652" s="14" t="s">
         <v>62</v>
       </c>
@@ -11020,7 +11024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A653" s="12" t="s">
         <v>63</v>
       </c>
@@ -11034,7 +11038,7 @@
         <v>48.38</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A654" s="14" t="s">
         <v>62</v>
       </c>
@@ -11048,7 +11052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A655" s="12" t="s">
         <v>63</v>
       </c>
@@ -11062,7 +11066,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A656" s="14" t="s">
         <v>62</v>
       </c>
@@ -11076,7 +11080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A657" s="12" t="s">
         <v>63</v>
       </c>
@@ -11090,7 +11094,7 @@
         <v>50.97</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A658" s="14" t="s">
         <v>62</v>
       </c>
@@ -11104,7 +11108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A659" s="12" t="s">
         <v>63</v>
       </c>
@@ -11118,7 +11122,7 @@
         <v>45.63</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A660" s="14" t="s">
         <v>62</v>
       </c>
@@ -11132,7 +11136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A661" s="12" t="s">
         <v>63</v>
       </c>
@@ -11146,7 +11150,7 @@
         <v>49.15</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A662" s="14" t="s">
         <v>62</v>
       </c>
@@ -11160,7 +11164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A663" s="12" t="s">
         <v>63</v>
       </c>
@@ -11174,7 +11178,7 @@
         <v>44.99</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A664" s="14" t="s">
         <v>62</v>
       </c>
@@ -11188,7 +11192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A665" s="12" t="s">
         <v>63</v>
       </c>
@@ -11202,7 +11206,7 @@
         <v>46.28</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A666" s="14" t="s">
         <v>62</v>
       </c>
@@ -11216,7 +11220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A667" s="12" t="s">
         <v>63</v>
       </c>
@@ -11230,7 +11234,7 @@
         <v>40.03</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A668" s="14" t="s">
         <v>62</v>
       </c>
@@ -11244,7 +11248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A669" s="12" t="s">
         <v>63</v>
       </c>
@@ -11258,7 +11262,7 @@
         <v>44.96</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A670" s="14" t="s">
         <v>62</v>
       </c>
@@ -11272,7 +11276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A671" s="12" t="s">
         <v>63</v>
       </c>
@@ -11286,7 +11290,7 @@
         <v>44.16</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A672" s="14" t="s">
         <v>62</v>
       </c>
@@ -11300,7 +11304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A673" s="12" t="s">
         <v>63</v>
       </c>
@@ -11314,7 +11318,7 @@
         <v>45.73</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A674" s="14" t="s">
         <v>62</v>
       </c>
@@ -11328,7 +11332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A675" s="12" t="s">
         <v>63</v>
       </c>
@@ -11342,7 +11346,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A676" s="14" t="s">
         <v>62</v>
       </c>
@@ -11356,7 +11360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A677" s="12" t="s">
         <v>63</v>
       </c>
@@ -11370,7 +11374,7 @@
         <v>42.14</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A678" s="14" t="s">
         <v>62</v>
       </c>
@@ -11384,7 +11388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A679" s="12" t="s">
         <v>63</v>
       </c>
@@ -11398,7 +11402,7 @@
         <v>43.72</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A680" s="14" t="s">
         <v>62</v>
       </c>
@@ -11412,7 +11416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A681" s="12" t="s">
         <v>63</v>
       </c>
@@ -11426,7 +11430,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A682" s="14" t="s">
         <v>62</v>
       </c>
@@ -11440,7 +11444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A683" s="12" t="s">
         <v>63</v>
       </c>
@@ -11454,7 +11458,7 @@
         <v>37.03</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A684" s="14" t="s">
         <v>62</v>
       </c>
@@ -11468,7 +11472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A685" s="12" t="s">
         <v>63</v>
       </c>
@@ -11482,7 +11486,7 @@
         <v>37.76</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A686" s="14" t="s">
         <v>62</v>
       </c>
@@ -11496,7 +11500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A687" s="12" t="s">
         <v>63</v>
       </c>
@@ -11510,7 +11514,7 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A688" s="14" t="s">
         <v>62</v>
       </c>
@@ -11524,7 +11528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A689" s="12" t="s">
         <v>63</v>
       </c>
@@ -11538,7 +11542,7 @@
         <v>38.14</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A690" s="14" t="s">
         <v>62</v>
       </c>
@@ -11552,7 +11556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A691" s="12" t="s">
         <v>63</v>
       </c>
@@ -11566,7 +11570,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A692" s="14" t="s">
         <v>62</v>
       </c>
@@ -11580,7 +11584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A693" s="12" t="s">
         <v>63</v>
       </c>
@@ -11594,7 +11598,7 @@
         <v>42.79</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A694" s="14" t="s">
         <v>62</v>
       </c>
@@ -11608,7 +11612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A695" s="12" t="s">
         <v>63</v>
       </c>
@@ -11622,7 +11626,7 @@
         <v>42.99</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A696" s="14" t="s">
         <v>62</v>
       </c>
@@ -11636,7 +11640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A697" s="12" t="s">
         <v>63</v>
       </c>
@@ -11650,7 +11654,7 @@
         <v>51.25</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A698" s="14" t="s">
         <v>62</v>
       </c>
